--- a/Data/RemapDrafts/NilouRemapDraft.xlsx
+++ b/Data/RemapDrafts/NilouRemapDraft.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6146D5B0-DB6C-49F1-AE9F-E556F67B4E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8E7FDA-920B-4052-956B-56E278F4FD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{758608A3-4F21-4B81-A842-759D09A24DF2}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.8 Nilou to NilouBreeze" sheetId="1" r:id="rId1"/>
-    <sheet name="V4.8 NilouBreeze to Nilou" sheetId="2" r:id="rId2"/>
+    <sheet name="Credits" sheetId="3" r:id="rId1"/>
+    <sheet name="V4.8 Nilou to NilouBreeze" sheetId="1" r:id="rId2"/>
+    <sheet name="V4.8 NilouBreeze to Nilou" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.8 Nilou to NilouBreeze'!$A$1:$D$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.8 NilouBreeze to Nilou'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.8 Nilou to NilouBreeze'!$A$1:$D$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'V4.8 NilouBreeze to Nilou'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
   <si>
     <t>Nilou</t>
   </si>
@@ -224,13 +225,22 @@
   </si>
   <si>
     <t>NilouBreeze's vision near right waist</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +251,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -264,14 +290,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -624,6 +654,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0EE8BCE-AB2F-4E9F-9D9D-1621ABF2A3F5}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{E6109183-6159-4A4F-A455-F89DB41E87FE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{647A9EC2-C0C3-426F-AEF9-8960EFB12B32}">
   <dimension ref="A1:D136"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1957,7 +2018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2813BAF5-CA0C-44C8-B251-E4F12999A3E4}">
   <dimension ref="A1:D128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
